--- a/PHPExcel/Examples/Format_CPE_COMPRAS.xlsx
+++ b/PHPExcel/Examples/Format_CPE_COMPRAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miguel Sanchez\AppData\Local\Temp\fz3temp-5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\clinicasaludmadreymujer\PHPExcel\Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA44AC1-F666-463D-846A-75B6A5575ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DB44FA-3EE8-413D-A58C-B691514256A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="-120" windowWidth="37455" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" Registro de Ingresos" sheetId="8" r:id="rId1"/>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -171,13 +169,13 @@
     <t>Tarjeta</t>
   </si>
   <si>
-    <t>CENTRO MEDICO ESPECIALIZADO SALUD MADRE &amp; MUJER S.A.C.</t>
-  </si>
-  <si>
-    <t>CAL.EL VIRREY NRO. 125 URB. BANCARIOS LAMBAYEQUE - CHICLAYO - CHICLAYO</t>
-  </si>
-  <si>
     <t>Comisión</t>
+  </si>
+  <si>
+    <t>CLINICA ENFOQUE SALUD</t>
+  </si>
+  <si>
+    <t>AV. ALFONSO UGARTE #673 LAMBAYEQUE - CHICLAYO - CHICLAYO</t>
   </si>
 </sst>
 </file>
@@ -189,7 +187,7 @@
     <numFmt numFmtId="164" formatCode="000000"/>
     <numFmt numFmtId="165" formatCode="00000000"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -766,6 +764,8 @@
     </xf>
     <xf numFmtId="44" fontId="32" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="33" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -796,6 +796,24 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="14" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="15" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -811,26 +829,6 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="14" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="15" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1163,7 +1161,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" style="1" customWidth="1"/>
@@ -1187,24 +1185,24 @@
     <col min="22" max="16384" width="11.42578125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="20.25" customHeight="1" thickBot="1">
       <c r="A1" s="5"/>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55" t="s">
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="56"/>
+      <c r="H1" s="58"/>
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="19.5" thickBot="1">
       <c r="A2" s="6"/>
       <c r="B2" s="35"/>
       <c r="C2" s="36"/>
@@ -1220,19 +1218,19 @@
       <c r="K2" s="28"/>
       <c r="L2" s="28"/>
     </row>
-    <row r="3" spans="1:19" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="59" t="s">
+    <row r="3" spans="1:19" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A3" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="74" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
       <c r="I3" s="50">
         <v>1</v>
       </c>
@@ -1240,53 +1238,51 @@
       <c r="K3" s="12"/>
       <c r="L3" s="18"/>
     </row>
-    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
+    <row r="4" spans="1:19" ht="15.75">
+      <c r="A4" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:19" s="47" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+    <row r="5" spans="1:19" s="47" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A5" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="44">
-        <v>20609746387</v>
-      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
       <c r="J5" s="44"/>
       <c r="K5" s="44"/>
       <c r="L5" s="46"/>
     </row>
-    <row r="6" spans="1:19" s="47" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" s="47" customFormat="1" ht="14.25" customHeight="1">
       <c r="A6" s="43"/>
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="43"/>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="53"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="45"/>
       <c r="H6" s="45"/>
       <c r="I6" s="45"/>
@@ -1294,15 +1290,15 @@
       <c r="K6" s="44"/>
       <c r="L6" s="46"/>
     </row>
-    <row r="7" spans="1:19" s="5" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" s="5" customFormat="1" ht="12" hidden="1" customHeight="1">
       <c r="A7" s="41"/>
       <c r="B7" s="42"/>
       <c r="E7" s="48"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="74"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="53"/>
       <c r="H7" s="45"/>
     </row>
-    <row r="8" spans="1:19" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" s="5" customFormat="1" ht="18" customHeight="1">
       <c r="A8" s="29" t="s">
         <v>41</v>
       </c>
@@ -1322,11 +1318,11 @@
         <v>43</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H8" s="45"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19">
       <c r="A9" s="17"/>
       <c r="B9" s="31"/>
       <c r="C9" s="32"/>
@@ -1359,7 +1355,7 @@
     <mergeCell ref="C3:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.12" top="0.35" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="62" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1370,7 +1366,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
@@ -1395,24 +1391,24 @@
     <col min="21" max="16384" width="11.42578125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="20.25">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
-      <c r="F1" s="63" t="s">
+      <c r="F1" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-    </row>
-    <row r="2" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+    </row>
+    <row r="2" spans="1:20" ht="18.75">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1427,139 +1423,139 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="61" t="s">
+    <row r="3" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A3" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="66" t="s">
+      <c r="B3" s="63"/>
+      <c r="C3" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
       <c r="M3" s="26"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
+    <row r="4" spans="1:20" ht="15.75">
+      <c r="A4" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="64" t="s">
+      <c r="B4" s="63"/>
+      <c r="C4" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
       <c r="M4" s="7"/>
     </row>
-    <row r="5" spans="1:20" ht="33" x14ac:dyDescent="0.25">
-      <c r="A5" s="62" t="s">
+    <row r="5" spans="1:20" ht="33">
+      <c r="A5" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="65">
+      <c r="B5" s="70"/>
+      <c r="C5" s="73">
         <v>20488089219</v>
       </c>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
       <c r="G5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="15" customHeight="1">
       <c r="A6" s="30"/>
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="72" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="71" t="s">
+      <c r="H6" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="67" t="s">
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="70" t="s">
+      <c r="L6" s="64"/>
+      <c r="M6" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="67" t="s">
+      <c r="N6" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="O6" s="67"/>
-      <c r="P6" s="70" t="s">
+      <c r="O6" s="64"/>
+      <c r="P6" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="Q6" s="67" t="s">
+      <c r="Q6" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-    </row>
-    <row r="7" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+      <c r="R6" s="64"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="64"/>
+    </row>
+    <row r="7" spans="1:20" ht="21" customHeight="1">
+      <c r="A7" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="71" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71" t="s">
+      <c r="I7" s="68"/>
+      <c r="J7" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="67"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="67"/>
-      <c r="R7" s="67"/>
-      <c r="S7" s="67"/>
-      <c r="T7" s="67"/>
-    </row>
-    <row r="8" spans="1:20" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="69"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
+      <c r="K7" s="64"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="64"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="64"/>
+    </row>
+    <row r="8" spans="1:20" ht="117.75" customHeight="1">
+      <c r="A8" s="66"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
       <c r="D8" s="2" t="s">
         <v>13</v>
       </c>
@@ -1569,28 +1565,28 @@
       <c r="F8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="72"/>
+      <c r="G8" s="69"/>
       <c r="H8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="71"/>
+      <c r="J8" s="68"/>
       <c r="K8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="70"/>
+      <c r="M8" s="67"/>
       <c r="N8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="70"/>
+      <c r="P8" s="67"/>
       <c r="Q8" s="4" t="s">
         <v>22</v>
       </c>
@@ -1604,7 +1600,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" s="17"/>
       <c r="B9" s="8"/>
       <c r="C9" s="9"/>
@@ -1628,6 +1624,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="C3:J3"/>
     <mergeCell ref="Q6:T7"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="K6:L7"/>
@@ -1641,16 +1645,8 @@
     <mergeCell ref="D6:F7"/>
     <mergeCell ref="G6:G8"/>
     <mergeCell ref="H6:J6"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="C3:J3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.12" top="0.35" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>